--- a/artfynd/A 51212-2022 artfynd.xlsx
+++ b/artfynd/A 51212-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747346</v>
+        <v>122747345</v>
       </c>
       <c r="B2" t="n">
-        <v>79872</v>
+        <v>91511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609192</v>
+        <v>609203</v>
       </c>
       <c r="R2" t="n">
         <v>7063705</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747345</v>
+        <v>122747346</v>
       </c>
       <c r="B3" t="n">
-        <v>91507</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609203</v>
+        <v>609192</v>
       </c>
       <c r="R3" t="n">
         <v>7063705</v>
@@ -890,7 +890,7 @@
         <v>122747347</v>
       </c>
       <c r="B4" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51212-2022 artfynd.xlsx
+++ b/artfynd/A 51212-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747345</v>
+        <v>122747347</v>
       </c>
       <c r="B2" t="n">
-        <v>91511</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609203</v>
+        <v>609194</v>
       </c>
       <c r="R2" t="n">
-        <v>7063705</v>
+        <v>7063711</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747346</v>
+        <v>122747345</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>91511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609192</v>
+        <v>609203</v>
       </c>
       <c r="R3" t="n">
         <v>7063705</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747347</v>
+        <v>122747346</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609194</v>
+        <v>609192</v>
       </c>
       <c r="R4" t="n">
-        <v>7063711</v>
+        <v>7063705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51212-2022 artfynd.xlsx
+++ b/artfynd/A 51212-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747345</v>
+        <v>122747346</v>
       </c>
       <c r="B3" t="n">
-        <v>91511</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609203</v>
+        <v>609192</v>
       </c>
       <c r="R3" t="n">
         <v>7063705</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747346</v>
+        <v>122747345</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>91511</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609192</v>
+        <v>609203</v>
       </c>
       <c r="R4" t="n">
         <v>7063705</v>

--- a/artfynd/A 51212-2022 artfynd.xlsx
+++ b/artfynd/A 51212-2022 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747345</v>
       </c>
       <c r="B4" t="n">
-        <v>91511</v>
+        <v>91519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51212-2022 artfynd.xlsx
+++ b/artfynd/A 51212-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747347</v>
+        <v>122747345</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>91519</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609194</v>
+        <v>609203</v>
       </c>
       <c r="R2" t="n">
-        <v>7063711</v>
+        <v>7063705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747345</v>
+        <v>122747347</v>
       </c>
       <c r="B4" t="n">
-        <v>91519</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609203</v>
+        <v>609194</v>
       </c>
       <c r="R4" t="n">
-        <v>7063705</v>
+        <v>7063711</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51212-2022 artfynd.xlsx
+++ b/artfynd/A 51212-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747346</v>
+        <v>122747347</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609192</v>
+        <v>609194</v>
       </c>
       <c r="R3" t="n">
-        <v>7063705</v>
+        <v>7063711</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747347</v>
+        <v>122747346</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609194</v>
+        <v>609192</v>
       </c>
       <c r="R4" t="n">
-        <v>7063711</v>
+        <v>7063705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51212-2022 artfynd.xlsx
+++ b/artfynd/A 51212-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747345</v>
       </c>
       <c r="B2" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747347</v>
+        <v>122747346</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79879</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609194</v>
+        <v>609192</v>
       </c>
       <c r="R3" t="n">
-        <v>7063711</v>
+        <v>7063705</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747346</v>
+        <v>122747347</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609192</v>
+        <v>609194</v>
       </c>
       <c r="R4" t="n">
-        <v>7063705</v>
+        <v>7063711</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51212-2022 artfynd.xlsx
+++ b/artfynd/A 51212-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747345</v>
+        <v>122747347</v>
       </c>
       <c r="B2" t="n">
-        <v>91522</v>
+        <v>79852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609203</v>
+        <v>609194</v>
       </c>
       <c r="R2" t="n">
-        <v>7063705</v>
+        <v>7063711</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask, Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747346</v>
+        <v>122747345</v>
       </c>
       <c r="B3" t="n">
-        <v>79879</v>
+        <v>91524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609192</v>
+        <v>609203</v>
       </c>
       <c r="R3" t="n">
         <v>7063705</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask, Helene Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747347</v>
+        <v>122747346</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>79881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609194</v>
+        <v>609192</v>
       </c>
       <c r="R4" t="n">
-        <v>7063711</v>
+        <v>7063705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask, Helene Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 51212-2022 artfynd.xlsx
+++ b/artfynd/A 51212-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747347</v>
+        <v>122747345</v>
       </c>
       <c r="B2" t="n">
-        <v>80437</v>
+        <v>92546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609194</v>
+        <v>609203</v>
       </c>
       <c r="R2" t="n">
-        <v>7063711</v>
+        <v>7063705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747345</v>
+        <v>122747347</v>
       </c>
       <c r="B3" t="n">
-        <v>92516</v>
+        <v>80488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609203</v>
+        <v>609194</v>
       </c>
       <c r="R3" t="n">
-        <v>7063705</v>
+        <v>7063711</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747346</v>
+        <v>122747348</v>
       </c>
       <c r="B4" t="n">
-        <v>80466</v>
+        <v>80488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609192</v>
+        <v>609187</v>
       </c>
       <c r="R4" t="n">
-        <v>7063705</v>
+        <v>7063757</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,6 +971,107 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122747346</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>N Oxmyran S, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>609192</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7063705</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 51212-2022 artfynd.xlsx
+++ b/artfynd/A 51212-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747345</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747347</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747348</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747346</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>